--- a/artfynd/A 31163-2019 artfynd.xlsx
+++ b/artfynd/A 31163-2019 artfynd.xlsx
@@ -1311,10 +1311,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>113271052</v>
+        <v>113271059</v>
       </c>
       <c r="B8" t="n">
-        <v>96264</v>
+        <v>97298</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1323,25 +1323,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>221946</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Mattlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lycopodium clavatum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1351,10 +1351,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>578320</v>
+        <v>578425</v>
       </c>
       <c r="R8" t="n">
-        <v>6653021</v>
+        <v>6653063</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1397,6 +1397,11 @@
       </c>
       <c r="AG8" t="b">
         <v>0</v>
+      </c>
+      <c r="AO8" t="inlineStr">
+        <is>
+          <t>15 ex</t>
+        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
@@ -1417,10 +1422,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>113270997</v>
+        <v>113271052</v>
       </c>
       <c r="B9" t="n">
-        <v>90029</v>
+        <v>96264</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1429,25 +1434,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1202</v>
+        <v>221946</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Mattlummer</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lycopodium clavatum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1457,10 +1462,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>578266</v>
+        <v>578320</v>
       </c>
       <c r="R9" t="n">
-        <v>6653054</v>
+        <v>6653021</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1523,10 +1528,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>113271059</v>
+        <v>113270997</v>
       </c>
       <c r="B10" t="n">
-        <v>97298</v>
+        <v>90029</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1535,25 +1540,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1563,10 +1568,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>578425</v>
+        <v>578266</v>
       </c>
       <c r="R10" t="n">
-        <v>6653063</v>
+        <v>6653054</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1609,11 +1614,6 @@
       </c>
       <c r="AG10" t="b">
         <v>0</v>
-      </c>
-      <c r="AO10" t="inlineStr">
-        <is>
-          <t>15 ex</t>
-        </is>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">

--- a/artfynd/A 31163-2019 artfynd.xlsx
+++ b/artfynd/A 31163-2019 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>113270999</v>
+        <v>113271119</v>
       </c>
       <c r="B2" t="n">
-        <v>90029</v>
+        <v>5164</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1202</v>
+        <v>100526</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>578412</v>
+        <v>578340</v>
       </c>
       <c r="R2" t="n">
-        <v>6653031</v>
+        <v>6653073</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>113271119</v>
+        <v>113271052</v>
       </c>
       <c r="B3" t="n">
-        <v>5164</v>
+        <v>96280</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -797,21 +797,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100526</v>
+        <v>221946</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Mattlummer</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Lycopodium clavatum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -821,10 +821,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>578340</v>
+        <v>578320</v>
       </c>
       <c r="R3" t="n">
-        <v>6653073</v>
+        <v>6653021</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -887,10 +887,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>113271120</v>
+        <v>113270998</v>
       </c>
       <c r="B4" t="n">
-        <v>5164</v>
+        <v>90045</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -899,25 +899,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100526</v>
+        <v>1202</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -927,10 +927,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>578439</v>
+        <v>578329</v>
       </c>
       <c r="R4" t="n">
-        <v>6653082</v>
+        <v>6653058</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -993,10 +993,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>113270962</v>
+        <v>113271110</v>
       </c>
       <c r="B5" t="n">
-        <v>89993</v>
+        <v>91306</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1009,21 +1009,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5447</v>
+        <v>4364</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1033,10 +1033,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>578431</v>
+        <v>578437</v>
       </c>
       <c r="R5" t="n">
-        <v>6653031</v>
+        <v>6653081</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1099,10 +1099,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>113271110</v>
+        <v>113270999</v>
       </c>
       <c r="B6" t="n">
-        <v>91290</v>
+        <v>90045</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1111,25 +1111,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>4364</v>
+        <v>1202</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1139,10 +1139,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>578437</v>
+        <v>578412</v>
       </c>
       <c r="R6" t="n">
-        <v>6653081</v>
+        <v>6653031</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1205,10 +1205,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>113270998</v>
+        <v>113270962</v>
       </c>
       <c r="B7" t="n">
-        <v>90029</v>
+        <v>90009</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1217,25 +1217,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1202</v>
+        <v>5447</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1245,10 +1245,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>578329</v>
+        <v>578431</v>
       </c>
       <c r="R7" t="n">
-        <v>6653058</v>
+        <v>6653031</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1311,10 +1311,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>113271059</v>
+        <v>113271120</v>
       </c>
       <c r="B8" t="n">
-        <v>97298</v>
+        <v>5164</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1323,25 +1323,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>100526</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1351,10 +1351,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>578425</v>
+        <v>578439</v>
       </c>
       <c r="R8" t="n">
-        <v>6653063</v>
+        <v>6653082</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1397,11 +1397,6 @@
       </c>
       <c r="AG8" t="b">
         <v>0</v>
-      </c>
-      <c r="AO8" t="inlineStr">
-        <is>
-          <t>15 ex</t>
-        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
@@ -1422,10 +1417,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>113271052</v>
+        <v>113271059</v>
       </c>
       <c r="B9" t="n">
-        <v>96264</v>
+        <v>97314</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1434,25 +1429,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>221946</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Mattlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lycopodium clavatum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1462,10 +1457,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>578320</v>
+        <v>578425</v>
       </c>
       <c r="R9" t="n">
-        <v>6653021</v>
+        <v>6653063</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1508,6 +1503,11 @@
       </c>
       <c r="AG9" t="b">
         <v>0</v>
+      </c>
+      <c r="AO9" t="inlineStr">
+        <is>
+          <t>15 ex</t>
+        </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
@@ -1531,7 +1531,7 @@
         <v>113270997</v>
       </c>
       <c r="B10" t="n">
-        <v>90029</v>
+        <v>90045</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>

--- a/artfynd/A 31163-2019 artfynd.xlsx
+++ b/artfynd/A 31163-2019 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>113271119</v>
+        <v>113271059</v>
       </c>
       <c r="B2" t="n">
-        <v>5164</v>
+        <v>97314</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100526</v>
+        <v>220787</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>578340</v>
+        <v>578425</v>
       </c>
       <c r="R2" t="n">
-        <v>6653073</v>
+        <v>6653063</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -761,6 +761,11 @@
       </c>
       <c r="AG2" t="b">
         <v>0</v>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>15 ex</t>
+        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
@@ -781,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>113271052</v>
+        <v>113270997</v>
       </c>
       <c r="B3" t="n">
-        <v>96280</v>
+        <v>90045</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,25 +798,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221946</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Mattlummer</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lycopodium clavatum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -821,10 +826,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>578320</v>
+        <v>578266</v>
       </c>
       <c r="R3" t="n">
-        <v>6653021</v>
+        <v>6653054</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -993,10 +998,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>113271110</v>
+        <v>113271052</v>
       </c>
       <c r="B5" t="n">
-        <v>91306</v>
+        <v>96280</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1009,21 +1014,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4364</v>
+        <v>221946</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Mattlummer</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Lycopodium clavatum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1033,10 +1038,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>578437</v>
+        <v>578320</v>
       </c>
       <c r="R5" t="n">
-        <v>6653081</v>
+        <v>6653021</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1099,10 +1104,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>113270999</v>
+        <v>113271119</v>
       </c>
       <c r="B6" t="n">
-        <v>90045</v>
+        <v>5164</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1111,25 +1116,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1202</v>
+        <v>100526</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1139,10 +1144,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>578412</v>
+        <v>578340</v>
       </c>
       <c r="R6" t="n">
-        <v>6653031</v>
+        <v>6653073</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1311,10 +1316,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>113271120</v>
+        <v>113271110</v>
       </c>
       <c r="B8" t="n">
-        <v>5164</v>
+        <v>91306</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1327,21 +1332,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100526</v>
+        <v>4364</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1351,10 +1356,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>578439</v>
+        <v>578437</v>
       </c>
       <c r="R8" t="n">
-        <v>6653082</v>
+        <v>6653081</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1417,10 +1422,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>113271059</v>
+        <v>113270999</v>
       </c>
       <c r="B9" t="n">
-        <v>97314</v>
+        <v>90045</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1429,25 +1434,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1457,10 +1462,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>578425</v>
+        <v>578412</v>
       </c>
       <c r="R9" t="n">
-        <v>6653063</v>
+        <v>6653031</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1503,11 +1508,6 @@
       </c>
       <c r="AG9" t="b">
         <v>0</v>
-      </c>
-      <c r="AO9" t="inlineStr">
-        <is>
-          <t>15 ex</t>
-        </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
@@ -1528,10 +1528,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>113270997</v>
+        <v>113271120</v>
       </c>
       <c r="B10" t="n">
-        <v>90045</v>
+        <v>5164</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1540,25 +1540,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1202</v>
+        <v>100526</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1568,10 +1568,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>578266</v>
+        <v>578439</v>
       </c>
       <c r="R10" t="n">
-        <v>6653054</v>
+        <v>6653082</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>

--- a/artfynd/A 31163-2019 artfynd.xlsx
+++ b/artfynd/A 31163-2019 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>113271059</v>
+        <v>113271119</v>
       </c>
       <c r="B2" t="n">
-        <v>97314</v>
+        <v>5164</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>100526</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>578425</v>
+        <v>578340</v>
       </c>
       <c r="R2" t="n">
-        <v>6653063</v>
+        <v>6653073</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -761,11 +761,6 @@
       </c>
       <c r="AG2" t="b">
         <v>0</v>
-      </c>
-      <c r="AO2" t="inlineStr">
-        <is>
-          <t>15 ex</t>
-        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
@@ -786,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>113270997</v>
+        <v>113270962</v>
       </c>
       <c r="B3" t="n">
-        <v>90045</v>
+        <v>90021</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -798,25 +793,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1202</v>
+        <v>5447</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -826,10 +821,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>578266</v>
+        <v>578431</v>
       </c>
       <c r="R3" t="n">
-        <v>6653054</v>
+        <v>6653031</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -892,10 +887,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>113270998</v>
+        <v>113270997</v>
       </c>
       <c r="B4" t="n">
-        <v>90045</v>
+        <v>90057</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -932,10 +927,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>578329</v>
+        <v>578266</v>
       </c>
       <c r="R4" t="n">
-        <v>6653058</v>
+        <v>6653054</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -998,10 +993,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>113271052</v>
+        <v>113271120</v>
       </c>
       <c r="B5" t="n">
-        <v>96280</v>
+        <v>5164</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1014,21 +1009,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>221946</v>
+        <v>100526</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Mattlummer</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lycopodium clavatum</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1038,10 +1033,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>578320</v>
+        <v>578439</v>
       </c>
       <c r="R5" t="n">
-        <v>6653021</v>
+        <v>6653082</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1104,10 +1099,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>113271119</v>
+        <v>113270999</v>
       </c>
       <c r="B6" t="n">
-        <v>5164</v>
+        <v>90057</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1116,25 +1111,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100526</v>
+        <v>1202</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1144,10 +1139,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>578340</v>
+        <v>578412</v>
       </c>
       <c r="R6" t="n">
-        <v>6653073</v>
+        <v>6653031</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1210,10 +1205,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>113270962</v>
+        <v>113270998</v>
       </c>
       <c r="B7" t="n">
-        <v>90009</v>
+        <v>90057</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1222,25 +1217,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1250,10 +1245,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>578431</v>
+        <v>578329</v>
       </c>
       <c r="R7" t="n">
-        <v>6653031</v>
+        <v>6653058</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1316,10 +1311,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>113271110</v>
+        <v>113271059</v>
       </c>
       <c r="B8" t="n">
-        <v>91306</v>
+        <v>97326</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1328,25 +1323,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1356,10 +1351,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>578437</v>
+        <v>578425</v>
       </c>
       <c r="R8" t="n">
-        <v>6653081</v>
+        <v>6653063</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1402,6 +1397,11 @@
       </c>
       <c r="AG8" t="b">
         <v>0</v>
+      </c>
+      <c r="AO8" t="inlineStr">
+        <is>
+          <t>15 ex</t>
+        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
@@ -1422,10 +1422,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>113270999</v>
+        <v>113271052</v>
       </c>
       <c r="B9" t="n">
-        <v>90045</v>
+        <v>96292</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1434,25 +1434,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1202</v>
+        <v>221946</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Mattlummer</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lycopodium clavatum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1462,10 +1462,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>578412</v>
+        <v>578320</v>
       </c>
       <c r="R9" t="n">
-        <v>6653031</v>
+        <v>6653021</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1528,10 +1528,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>113271120</v>
+        <v>113271110</v>
       </c>
       <c r="B10" t="n">
-        <v>5164</v>
+        <v>91318</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1544,21 +1544,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100526</v>
+        <v>4364</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1568,10 +1568,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>578439</v>
+        <v>578437</v>
       </c>
       <c r="R10" t="n">
-        <v>6653082</v>
+        <v>6653081</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>

--- a/artfynd/A 31163-2019 artfynd.xlsx
+++ b/artfynd/A 31163-2019 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>113271119</v>
+        <v>113270962</v>
       </c>
       <c r="B2" t="n">
-        <v>5164</v>
+        <v>90021</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100526</v>
+        <v>5447</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>578340</v>
+        <v>578431</v>
       </c>
       <c r="R2" t="n">
-        <v>6653073</v>
+        <v>6653031</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>113270962</v>
+        <v>113271052</v>
       </c>
       <c r="B3" t="n">
-        <v>90021</v>
+        <v>96292</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -797,21 +797,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5447</v>
+        <v>221946</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Mattlummer</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Lycopodium clavatum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -821,10 +821,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>578431</v>
+        <v>578320</v>
       </c>
       <c r="R3" t="n">
-        <v>6653031</v>
+        <v>6653021</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -887,10 +887,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>113270997</v>
+        <v>113271120</v>
       </c>
       <c r="B4" t="n">
-        <v>90057</v>
+        <v>5164</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -899,25 +899,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1202</v>
+        <v>100526</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -927,10 +927,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>578266</v>
+        <v>578439</v>
       </c>
       <c r="R4" t="n">
-        <v>6653054</v>
+        <v>6653082</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -993,7 +993,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>113271120</v>
+        <v>113271119</v>
       </c>
       <c r="B5" t="n">
         <v>5164</v>
@@ -1033,10 +1033,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>578439</v>
+        <v>578340</v>
       </c>
       <c r="R5" t="n">
-        <v>6653082</v>
+        <v>6653073</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1099,10 +1099,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>113270999</v>
+        <v>113271059</v>
       </c>
       <c r="B6" t="n">
-        <v>90057</v>
+        <v>97326</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1111,25 +1111,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1139,10 +1139,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>578412</v>
+        <v>578425</v>
       </c>
       <c r="R6" t="n">
-        <v>6653031</v>
+        <v>6653063</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1185,6 +1185,11 @@
       </c>
       <c r="AG6" t="b">
         <v>0</v>
+      </c>
+      <c r="AO6" t="inlineStr">
+        <is>
+          <t>15 ex</t>
+        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
@@ -1205,7 +1210,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>113270998</v>
+        <v>113270997</v>
       </c>
       <c r="B7" t="n">
         <v>90057</v>
@@ -1245,10 +1250,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>578329</v>
+        <v>578266</v>
       </c>
       <c r="R7" t="n">
-        <v>6653058</v>
+        <v>6653054</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1311,10 +1316,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>113271059</v>
+        <v>113271110</v>
       </c>
       <c r="B8" t="n">
-        <v>97326</v>
+        <v>91318</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1323,25 +1328,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1351,10 +1356,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>578425</v>
+        <v>578437</v>
       </c>
       <c r="R8" t="n">
-        <v>6653063</v>
+        <v>6653081</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1397,11 +1402,6 @@
       </c>
       <c r="AG8" t="b">
         <v>0</v>
-      </c>
-      <c r="AO8" t="inlineStr">
-        <is>
-          <t>15 ex</t>
-        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
@@ -1422,10 +1422,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>113271052</v>
+        <v>113270999</v>
       </c>
       <c r="B9" t="n">
-        <v>96292</v>
+        <v>90057</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1434,25 +1434,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>221946</v>
+        <v>1202</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Mattlummer</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lycopodium clavatum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1462,10 +1462,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>578320</v>
+        <v>578412</v>
       </c>
       <c r="R9" t="n">
-        <v>6653021</v>
+        <v>6653031</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1528,10 +1528,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>113271110</v>
+        <v>113270998</v>
       </c>
       <c r="B10" t="n">
-        <v>91318</v>
+        <v>90057</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1540,25 +1540,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>4364</v>
+        <v>1202</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1568,10 +1568,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>578437</v>
+        <v>578329</v>
       </c>
       <c r="R10" t="n">
-        <v>6653081</v>
+        <v>6653058</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>

--- a/artfynd/A 31163-2019 artfynd.xlsx
+++ b/artfynd/A 31163-2019 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>113270962</v>
+        <v>113270997</v>
       </c>
       <c r="B2" t="n">
-        <v>90021</v>
+        <v>90079</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>578431</v>
+        <v>578266</v>
       </c>
       <c r="R2" t="n">
-        <v>6653031</v>
+        <v>6653054</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>113271052</v>
+        <v>113270999</v>
       </c>
       <c r="B3" t="n">
-        <v>96292</v>
+        <v>90079</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,25 +793,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221946</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Mattlummer</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lycopodium clavatum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -821,10 +821,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>578320</v>
+        <v>578412</v>
       </c>
       <c r="R3" t="n">
-        <v>6653021</v>
+        <v>6653031</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -887,10 +887,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>113271120</v>
+        <v>113271110</v>
       </c>
       <c r="B4" t="n">
-        <v>5164</v>
+        <v>91340</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -903,21 +903,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100526</v>
+        <v>4364</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -927,10 +927,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>578439</v>
+        <v>578437</v>
       </c>
       <c r="R4" t="n">
-        <v>6653082</v>
+        <v>6653081</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -993,7 +993,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>113271119</v>
+        <v>113271120</v>
       </c>
       <c r="B5" t="n">
         <v>5164</v>
@@ -1033,10 +1033,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>578340</v>
+        <v>578439</v>
       </c>
       <c r="R5" t="n">
-        <v>6653073</v>
+        <v>6653082</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1099,10 +1099,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>113271059</v>
+        <v>113270962</v>
       </c>
       <c r="B6" t="n">
-        <v>97326</v>
+        <v>90043</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1111,25 +1111,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1139,10 +1139,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>578425</v>
+        <v>578431</v>
       </c>
       <c r="R6" t="n">
-        <v>6653063</v>
+        <v>6653031</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1185,11 +1185,6 @@
       </c>
       <c r="AG6" t="b">
         <v>0</v>
-      </c>
-      <c r="AO6" t="inlineStr">
-        <is>
-          <t>15 ex</t>
-        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
@@ -1210,10 +1205,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>113270997</v>
+        <v>113271059</v>
       </c>
       <c r="B7" t="n">
-        <v>90057</v>
+        <v>97348</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1222,25 +1217,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1250,10 +1245,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>578266</v>
+        <v>578425</v>
       </c>
       <c r="R7" t="n">
-        <v>6653054</v>
+        <v>6653063</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1296,6 +1291,11 @@
       </c>
       <c r="AG7" t="b">
         <v>0</v>
+      </c>
+      <c r="AO7" t="inlineStr">
+        <is>
+          <t>15 ex</t>
+        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
@@ -1316,10 +1316,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>113271110</v>
+        <v>113270998</v>
       </c>
       <c r="B8" t="n">
-        <v>91318</v>
+        <v>90079</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1328,25 +1328,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>4364</v>
+        <v>1202</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1356,10 +1356,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>578437</v>
+        <v>578329</v>
       </c>
       <c r="R8" t="n">
-        <v>6653081</v>
+        <v>6653058</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1422,10 +1422,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>113270999</v>
+        <v>113271119</v>
       </c>
       <c r="B9" t="n">
-        <v>90057</v>
+        <v>5164</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1434,25 +1434,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1202</v>
+        <v>100526</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1462,10 +1462,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>578412</v>
+        <v>578340</v>
       </c>
       <c r="R9" t="n">
-        <v>6653031</v>
+        <v>6653073</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1528,10 +1528,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>113270998</v>
+        <v>113271052</v>
       </c>
       <c r="B10" t="n">
-        <v>90057</v>
+        <v>96314</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1540,25 +1540,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1202</v>
+        <v>221946</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Mattlummer</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lycopodium clavatum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1568,10 +1568,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>578329</v>
+        <v>578320</v>
       </c>
       <c r="R10" t="n">
-        <v>6653058</v>
+        <v>6653021</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>

--- a/artfynd/A 31163-2019 artfynd.xlsx
+++ b/artfynd/A 31163-2019 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>113270997</v>
+        <v>113270999</v>
       </c>
       <c r="B2" t="n">
-        <v>90079</v>
+        <v>90083</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>578266</v>
+        <v>578412</v>
       </c>
       <c r="R2" t="n">
-        <v>6653054</v>
+        <v>6653031</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>113270999</v>
+        <v>113270997</v>
       </c>
       <c r="B3" t="n">
-        <v>90079</v>
+        <v>90083</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -821,10 +821,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>578412</v>
+        <v>578266</v>
       </c>
       <c r="R3" t="n">
-        <v>6653031</v>
+        <v>6653054</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -887,10 +887,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>113271110</v>
+        <v>113271052</v>
       </c>
       <c r="B4" t="n">
-        <v>91340</v>
+        <v>96318</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -903,21 +903,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4364</v>
+        <v>221946</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Mattlummer</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Lycopodium clavatum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -927,10 +927,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>578437</v>
+        <v>578320</v>
       </c>
       <c r="R4" t="n">
-        <v>6653081</v>
+        <v>6653021</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -1099,10 +1099,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>113270962</v>
+        <v>113271059</v>
       </c>
       <c r="B6" t="n">
-        <v>90043</v>
+        <v>97352</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1111,25 +1111,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1139,10 +1139,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>578431</v>
+        <v>578425</v>
       </c>
       <c r="R6" t="n">
-        <v>6653031</v>
+        <v>6653063</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1185,6 +1185,11 @@
       </c>
       <c r="AG6" t="b">
         <v>0</v>
+      </c>
+      <c r="AO6" t="inlineStr">
+        <is>
+          <t>15 ex</t>
+        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
@@ -1205,10 +1210,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>113271059</v>
+        <v>113270998</v>
       </c>
       <c r="B7" t="n">
-        <v>97348</v>
+        <v>90083</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1217,25 +1222,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1245,10 +1250,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>578425</v>
+        <v>578329</v>
       </c>
       <c r="R7" t="n">
-        <v>6653063</v>
+        <v>6653058</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1291,11 +1296,6 @@
       </c>
       <c r="AG7" t="b">
         <v>0</v>
-      </c>
-      <c r="AO7" t="inlineStr">
-        <is>
-          <t>15 ex</t>
-        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
@@ -1316,10 +1316,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>113270998</v>
+        <v>113270962</v>
       </c>
       <c r="B8" t="n">
-        <v>90079</v>
+        <v>90047</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1328,25 +1328,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1202</v>
+        <v>5447</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1356,10 +1356,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>578329</v>
+        <v>578431</v>
       </c>
       <c r="R8" t="n">
-        <v>6653058</v>
+        <v>6653031</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1422,10 +1422,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>113271119</v>
+        <v>113271110</v>
       </c>
       <c r="B9" t="n">
-        <v>5164</v>
+        <v>91344</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1438,21 +1438,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100526</v>
+        <v>4364</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1462,10 +1462,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>578340</v>
+        <v>578437</v>
       </c>
       <c r="R9" t="n">
-        <v>6653073</v>
+        <v>6653081</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1528,10 +1528,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>113271052</v>
+        <v>113271119</v>
       </c>
       <c r="B10" t="n">
-        <v>96314</v>
+        <v>5164</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1544,21 +1544,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>221946</v>
+        <v>100526</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Mattlummer</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lycopodium clavatum</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1568,10 +1568,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>578320</v>
+        <v>578340</v>
       </c>
       <c r="R10" t="n">
-        <v>6653021</v>
+        <v>6653073</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>

--- a/artfynd/A 31163-2019 artfynd.xlsx
+++ b/artfynd/A 31163-2019 artfynd.xlsx
@@ -1210,10 +1210,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>113270998</v>
+        <v>113271110</v>
       </c>
       <c r="B7" t="n">
-        <v>90083</v>
+        <v>91344</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1222,25 +1222,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1202</v>
+        <v>4364</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1250,10 +1250,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>578329</v>
+        <v>578437</v>
       </c>
       <c r="R7" t="n">
-        <v>6653058</v>
+        <v>6653081</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1316,10 +1316,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>113270962</v>
+        <v>113270998</v>
       </c>
       <c r="B8" t="n">
-        <v>90047</v>
+        <v>90083</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1328,25 +1328,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1356,10 +1356,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>578431</v>
+        <v>578329</v>
       </c>
       <c r="R8" t="n">
-        <v>6653031</v>
+        <v>6653058</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1422,10 +1422,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>113271110</v>
+        <v>113270962</v>
       </c>
       <c r="B9" t="n">
-        <v>91344</v>
+        <v>90047</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1438,21 +1438,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>4364</v>
+        <v>5447</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1462,10 +1462,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>578437</v>
+        <v>578431</v>
       </c>
       <c r="R9" t="n">
-        <v>6653081</v>
+        <v>6653031</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>

--- a/artfynd/A 31163-2019 artfynd.xlsx
+++ b/artfynd/A 31163-2019 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>113270999</v>
+        <v>113271059</v>
       </c>
       <c r="B2" t="n">
-        <v>90083</v>
+        <v>97352</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>578412</v>
+        <v>578425</v>
       </c>
       <c r="R2" t="n">
-        <v>6653031</v>
+        <v>6653063</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -761,6 +761,11 @@
       </c>
       <c r="AG2" t="b">
         <v>0</v>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>15 ex</t>
+        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
@@ -781,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>113270997</v>
+        <v>113271110</v>
       </c>
       <c r="B3" t="n">
-        <v>90083</v>
+        <v>91344</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,25 +798,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1202</v>
+        <v>4364</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -821,10 +826,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>578266</v>
+        <v>578437</v>
       </c>
       <c r="R3" t="n">
-        <v>6653054</v>
+        <v>6653081</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -887,10 +892,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>113271052</v>
+        <v>113271120</v>
       </c>
       <c r="B4" t="n">
-        <v>96318</v>
+        <v>5164</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -903,21 +908,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>221946</v>
+        <v>100526</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Mattlummer</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lycopodium clavatum</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -927,10 +932,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>578320</v>
+        <v>578439</v>
       </c>
       <c r="R4" t="n">
-        <v>6653021</v>
+        <v>6653082</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -993,10 +998,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>113271120</v>
+        <v>113271052</v>
       </c>
       <c r="B5" t="n">
-        <v>5164</v>
+        <v>96318</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1009,21 +1014,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100526</v>
+        <v>221946</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Mattlummer</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Lycopodium clavatum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1033,10 +1038,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>578439</v>
+        <v>578320</v>
       </c>
       <c r="R5" t="n">
-        <v>6653082</v>
+        <v>6653021</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1099,10 +1104,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>113271059</v>
+        <v>113270997</v>
       </c>
       <c r="B6" t="n">
-        <v>97352</v>
+        <v>90083</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1111,25 +1116,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1139,10 +1144,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>578425</v>
+        <v>578266</v>
       </c>
       <c r="R6" t="n">
-        <v>6653063</v>
+        <v>6653054</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1185,11 +1190,6 @@
       </c>
       <c r="AG6" t="b">
         <v>0</v>
-      </c>
-      <c r="AO6" t="inlineStr">
-        <is>
-          <t>15 ex</t>
-        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
@@ -1210,10 +1210,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>113271110</v>
+        <v>113270998</v>
       </c>
       <c r="B7" t="n">
-        <v>91344</v>
+        <v>90083</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1222,25 +1222,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>4364</v>
+        <v>1202</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1250,10 +1250,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>578437</v>
+        <v>578329</v>
       </c>
       <c r="R7" t="n">
-        <v>6653081</v>
+        <v>6653058</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1316,10 +1316,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>113270998</v>
+        <v>113271119</v>
       </c>
       <c r="B8" t="n">
-        <v>90083</v>
+        <v>5164</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1328,25 +1328,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1202</v>
+        <v>100526</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1356,10 +1356,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>578329</v>
+        <v>578340</v>
       </c>
       <c r="R8" t="n">
-        <v>6653058</v>
+        <v>6653073</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1422,10 +1422,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>113270962</v>
+        <v>113270999</v>
       </c>
       <c r="B9" t="n">
-        <v>90047</v>
+        <v>90083</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1434,25 +1434,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1462,7 +1462,7 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>578431</v>
+        <v>578412</v>
       </c>
       <c r="R9" t="n">
         <v>6653031</v>
@@ -1528,10 +1528,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>113271119</v>
+        <v>113270962</v>
       </c>
       <c r="B10" t="n">
-        <v>5164</v>
+        <v>90047</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1544,21 +1544,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100526</v>
+        <v>5447</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1568,10 +1568,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>578340</v>
+        <v>578431</v>
       </c>
       <c r="R10" t="n">
-        <v>6653073</v>
+        <v>6653031</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>

--- a/artfynd/A 31163-2019 artfynd.xlsx
+++ b/artfynd/A 31163-2019 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>113271059</v>
+        <v>113271052</v>
       </c>
       <c r="B2" t="n">
-        <v>97352</v>
+        <v>96324</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>221946</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mattlummer</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium clavatum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>578425</v>
+        <v>578320</v>
       </c>
       <c r="R2" t="n">
-        <v>6653063</v>
+        <v>6653021</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -761,11 +761,6 @@
       </c>
       <c r="AG2" t="b">
         <v>0</v>
-      </c>
-      <c r="AO2" t="inlineStr">
-        <is>
-          <t>15 ex</t>
-        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
@@ -786,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>113271110</v>
+        <v>113271059</v>
       </c>
       <c r="B3" t="n">
-        <v>91344</v>
+        <v>97358</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -798,25 +793,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -826,10 +821,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>578437</v>
+        <v>578425</v>
       </c>
       <c r="R3" t="n">
-        <v>6653081</v>
+        <v>6653063</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -872,6 +867,11 @@
       </c>
       <c r="AG3" t="b">
         <v>0</v>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>15 ex</t>
+        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
@@ -998,10 +998,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>113271052</v>
+        <v>113270997</v>
       </c>
       <c r="B5" t="n">
-        <v>96318</v>
+        <v>90089</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1010,25 +1010,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>221946</v>
+        <v>1202</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Mattlummer</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lycopodium clavatum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1038,10 +1038,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>578320</v>
+        <v>578266</v>
       </c>
       <c r="R5" t="n">
-        <v>6653021</v>
+        <v>6653054</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1104,10 +1104,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>113270997</v>
+        <v>113271110</v>
       </c>
       <c r="B6" t="n">
-        <v>90083</v>
+        <v>91350</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1116,25 +1116,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1202</v>
+        <v>4364</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1144,10 +1144,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>578266</v>
+        <v>578437</v>
       </c>
       <c r="R6" t="n">
-        <v>6653054</v>
+        <v>6653081</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1210,10 +1210,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>113270998</v>
+        <v>113270962</v>
       </c>
       <c r="B7" t="n">
-        <v>90083</v>
+        <v>90053</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1222,25 +1222,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1202</v>
+        <v>5447</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1250,10 +1250,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>578329</v>
+        <v>578431</v>
       </c>
       <c r="R7" t="n">
-        <v>6653058</v>
+        <v>6653031</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1425,7 +1425,7 @@
         <v>113270999</v>
       </c>
       <c r="B9" t="n">
-        <v>90083</v>
+        <v>90089</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1528,10 +1528,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>113270962</v>
+        <v>113270998</v>
       </c>
       <c r="B10" t="n">
-        <v>90047</v>
+        <v>90089</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1540,25 +1540,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1568,10 +1568,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>578431</v>
+        <v>578329</v>
       </c>
       <c r="R10" t="n">
-        <v>6653031</v>
+        <v>6653058</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>

--- a/artfynd/A 31163-2019 artfynd.xlsx
+++ b/artfynd/A 31163-2019 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>113271052</v>
+        <v>113271119</v>
       </c>
       <c r="B2" t="n">
-        <v>96324</v>
+        <v>5164</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221946</v>
+        <v>100526</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Mattlummer</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lycopodium clavatum</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>578320</v>
+        <v>578340</v>
       </c>
       <c r="R2" t="n">
-        <v>6653021</v>
+        <v>6653073</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>113271059</v>
+        <v>113270998</v>
       </c>
       <c r="B3" t="n">
-        <v>97358</v>
+        <v>90089</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,25 +793,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -821,10 +821,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>578425</v>
+        <v>578329</v>
       </c>
       <c r="R3" t="n">
-        <v>6653063</v>
+        <v>6653058</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -867,11 +867,6 @@
       </c>
       <c r="AG3" t="b">
         <v>0</v>
-      </c>
-      <c r="AO3" t="inlineStr">
-        <is>
-          <t>15 ex</t>
-        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
@@ -892,10 +887,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>113271120</v>
+        <v>113271052</v>
       </c>
       <c r="B4" t="n">
-        <v>5164</v>
+        <v>96324</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -908,21 +903,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100526</v>
+        <v>221946</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Mattlummer</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Lycopodium clavatum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -932,10 +927,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>578439</v>
+        <v>578320</v>
       </c>
       <c r="R4" t="n">
-        <v>6653082</v>
+        <v>6653021</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -998,10 +993,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>113270997</v>
+        <v>113271059</v>
       </c>
       <c r="B5" t="n">
-        <v>90089</v>
+        <v>97358</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1010,25 +1005,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1038,10 +1033,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>578266</v>
+        <v>578425</v>
       </c>
       <c r="R5" t="n">
-        <v>6653054</v>
+        <v>6653063</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1084,6 +1079,11 @@
       </c>
       <c r="AG5" t="b">
         <v>0</v>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>15 ex</t>
+        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
@@ -1104,10 +1104,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>113271110</v>
+        <v>113270962</v>
       </c>
       <c r="B6" t="n">
-        <v>91350</v>
+        <v>90053</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1120,21 +1120,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>4364</v>
+        <v>5447</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1144,10 +1144,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>578437</v>
+        <v>578431</v>
       </c>
       <c r="R6" t="n">
-        <v>6653081</v>
+        <v>6653031</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1210,10 +1210,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>113270962</v>
+        <v>113270999</v>
       </c>
       <c r="B7" t="n">
-        <v>90053</v>
+        <v>90089</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1222,25 +1222,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1250,7 +1250,7 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>578431</v>
+        <v>578412</v>
       </c>
       <c r="R7" t="n">
         <v>6653031</v>
@@ -1316,7 +1316,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>113271119</v>
+        <v>113271120</v>
       </c>
       <c r="B8" t="n">
         <v>5164</v>
@@ -1356,10 +1356,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>578340</v>
+        <v>578439</v>
       </c>
       <c r="R8" t="n">
-        <v>6653073</v>
+        <v>6653082</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1422,10 +1422,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>113270999</v>
+        <v>113271110</v>
       </c>
       <c r="B9" t="n">
-        <v>90089</v>
+        <v>91350</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1434,25 +1434,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1202</v>
+        <v>4364</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1462,10 +1462,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>578412</v>
+        <v>578437</v>
       </c>
       <c r="R9" t="n">
-        <v>6653031</v>
+        <v>6653081</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1528,7 +1528,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>113270998</v>
+        <v>113270997</v>
       </c>
       <c r="B10" t="n">
         <v>90089</v>
@@ -1568,10 +1568,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>578329</v>
+        <v>578266</v>
       </c>
       <c r="R10" t="n">
-        <v>6653058</v>
+        <v>6653054</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>

--- a/artfynd/A 31163-2019 artfynd.xlsx
+++ b/artfynd/A 31163-2019 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>113271119</v>
+        <v>113270998</v>
       </c>
       <c r="B2" t="n">
-        <v>5164</v>
+        <v>90089</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100526</v>
+        <v>1202</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>578340</v>
+        <v>578329</v>
       </c>
       <c r="R2" t="n">
-        <v>6653073</v>
+        <v>6653058</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>113270998</v>
+        <v>113271119</v>
       </c>
       <c r="B3" t="n">
-        <v>90089</v>
+        <v>5164</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,25 +793,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1202</v>
+        <v>100526</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -821,10 +821,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>578329</v>
+        <v>578340</v>
       </c>
       <c r="R3" t="n">
-        <v>6653058</v>
+        <v>6653073</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>

--- a/artfynd/A 31163-2019 artfynd.xlsx
+++ b/artfynd/A 31163-2019 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>113270998</v>
+        <v>113270962</v>
       </c>
       <c r="B2" t="n">
-        <v>90089</v>
+        <v>90060</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1202</v>
+        <v>5447</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>578329</v>
+        <v>578431</v>
       </c>
       <c r="R2" t="n">
-        <v>6653058</v>
+        <v>6653031</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>113271119</v>
+        <v>113270998</v>
       </c>
       <c r="B3" t="n">
-        <v>5164</v>
+        <v>90096</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,25 +793,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100526</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -821,10 +821,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>578340</v>
+        <v>578329</v>
       </c>
       <c r="R3" t="n">
-        <v>6653073</v>
+        <v>6653058</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -887,10 +887,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>113271052</v>
+        <v>113270997</v>
       </c>
       <c r="B4" t="n">
-        <v>96324</v>
+        <v>90096</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -899,25 +899,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>221946</v>
+        <v>1202</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Mattlummer</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lycopodium clavatum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -927,10 +927,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>578320</v>
+        <v>578266</v>
       </c>
       <c r="R4" t="n">
-        <v>6653021</v>
+        <v>6653054</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -993,10 +993,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>113271059</v>
+        <v>113271120</v>
       </c>
       <c r="B5" t="n">
-        <v>97358</v>
+        <v>5164</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1005,25 +1005,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>100526</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1033,10 +1033,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>578425</v>
+        <v>578439</v>
       </c>
       <c r="R5" t="n">
-        <v>6653063</v>
+        <v>6653082</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1079,11 +1079,6 @@
       </c>
       <c r="AG5" t="b">
         <v>0</v>
-      </c>
-      <c r="AO5" t="inlineStr">
-        <is>
-          <t>15 ex</t>
-        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
@@ -1104,10 +1099,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>113270962</v>
+        <v>113271059</v>
       </c>
       <c r="B6" t="n">
-        <v>90053</v>
+        <v>97365</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1116,25 +1111,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1144,10 +1139,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>578431</v>
+        <v>578425</v>
       </c>
       <c r="R6" t="n">
-        <v>6653031</v>
+        <v>6653063</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1190,6 +1185,11 @@
       </c>
       <c r="AG6" t="b">
         <v>0</v>
+      </c>
+      <c r="AO6" t="inlineStr">
+        <is>
+          <t>15 ex</t>
+        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
@@ -1210,10 +1210,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>113270999</v>
+        <v>113271110</v>
       </c>
       <c r="B7" t="n">
-        <v>90089</v>
+        <v>91357</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1222,25 +1222,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1202</v>
+        <v>4364</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1250,10 +1250,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>578412</v>
+        <v>578437</v>
       </c>
       <c r="R7" t="n">
-        <v>6653031</v>
+        <v>6653081</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1316,10 +1316,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>113271120</v>
+        <v>113270999</v>
       </c>
       <c r="B8" t="n">
-        <v>5164</v>
+        <v>90096</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1328,25 +1328,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100526</v>
+        <v>1202</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1356,10 +1356,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>578439</v>
+        <v>578412</v>
       </c>
       <c r="R8" t="n">
-        <v>6653082</v>
+        <v>6653031</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1422,10 +1422,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>113271110</v>
+        <v>113271119</v>
       </c>
       <c r="B9" t="n">
-        <v>91350</v>
+        <v>5164</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1438,21 +1438,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>4364</v>
+        <v>100526</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1462,10 +1462,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>578437</v>
+        <v>578340</v>
       </c>
       <c r="R9" t="n">
-        <v>6653081</v>
+        <v>6653073</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1528,10 +1528,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>113270997</v>
+        <v>113271052</v>
       </c>
       <c r="B10" t="n">
-        <v>90089</v>
+        <v>96331</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1540,25 +1540,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1202</v>
+        <v>221946</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Mattlummer</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lycopodium clavatum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1568,10 +1568,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>578266</v>
+        <v>578320</v>
       </c>
       <c r="R10" t="n">
-        <v>6653054</v>
+        <v>6653021</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>

--- a/artfynd/A 31163-2019 artfynd.xlsx
+++ b/artfynd/A 31163-2019 artfynd.xlsx
@@ -1210,10 +1210,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>113271110</v>
+        <v>113270999</v>
       </c>
       <c r="B7" t="n">
-        <v>91357</v>
+        <v>90096</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1222,25 +1222,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>4364</v>
+        <v>1202</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1250,10 +1250,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>578437</v>
+        <v>578412</v>
       </c>
       <c r="R7" t="n">
-        <v>6653081</v>
+        <v>6653031</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1316,10 +1316,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>113270999</v>
+        <v>113271110</v>
       </c>
       <c r="B8" t="n">
-        <v>90096</v>
+        <v>91357</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1328,25 +1328,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1202</v>
+        <v>4364</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1356,10 +1356,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>578412</v>
+        <v>578437</v>
       </c>
       <c r="R8" t="n">
-        <v>6653031</v>
+        <v>6653081</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>

--- a/artfynd/A 31163-2019 artfynd.xlsx
+++ b/artfynd/A 31163-2019 artfynd.xlsx
@@ -1210,10 +1210,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>113270999</v>
+        <v>113271110</v>
       </c>
       <c r="B7" t="n">
-        <v>90096</v>
+        <v>91357</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1222,25 +1222,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1202</v>
+        <v>4364</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1250,10 +1250,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>578412</v>
+        <v>578437</v>
       </c>
       <c r="R7" t="n">
-        <v>6653031</v>
+        <v>6653081</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1316,10 +1316,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>113271110</v>
+        <v>113270999</v>
       </c>
       <c r="B8" t="n">
-        <v>91357</v>
+        <v>90096</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1328,25 +1328,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>4364</v>
+        <v>1202</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1356,10 +1356,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>578437</v>
+        <v>578412</v>
       </c>
       <c r="R8" t="n">
-        <v>6653081</v>
+        <v>6653031</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>

--- a/artfynd/A 31163-2019 artfynd.xlsx
+++ b/artfynd/A 31163-2019 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 31163-2019 artfynd.xlsx
+++ b/artfynd/A 31163-2019 artfynd.xlsx
@@ -1420,7 +1420,7 @@
         <v>113271059</v>
       </c>
       <c r="B9" t="n">
-        <v>97650</v>
+        <v>98357</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1450,7 +1450,19 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr"/>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Bergsjön, Vstm</t>
@@ -1501,6 +1513,7 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 31163-2019 artfynd.xlsx
+++ b/artfynd/A 31163-2019 artfynd.xlsx
@@ -1420,7 +1420,7 @@
         <v>113271059</v>
       </c>
       <c r="B9" t="n">
-        <v>98357</v>
+        <v>98365</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>

--- a/artfynd/A 31163-2019 artfynd.xlsx
+++ b/artfynd/A 31163-2019 artfynd.xlsx
@@ -1420,7 +1420,7 @@
         <v>113271059</v>
       </c>
       <c r="B9" t="n">
-        <v>98365</v>
+        <v>98368</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>

--- a/artfynd/A 31163-2019 artfynd.xlsx
+++ b/artfynd/A 31163-2019 artfynd.xlsx
@@ -1420,7 +1420,7 @@
         <v>113271059</v>
       </c>
       <c r="B9" t="n">
-        <v>98368</v>
+        <v>98370</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>

--- a/artfynd/A 31163-2019 artfynd.xlsx
+++ b/artfynd/A 31163-2019 artfynd.xlsx
@@ -1420,7 +1420,7 @@
         <v>113271059</v>
       </c>
       <c r="B9" t="n">
-        <v>98370</v>
+        <v>98376</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>

--- a/artfynd/A 31163-2019 artfynd.xlsx
+++ b/artfynd/A 31163-2019 artfynd.xlsx
@@ -1420,7 +1420,7 @@
         <v>113271059</v>
       </c>
       <c r="B9" t="n">
-        <v>98379</v>
+        <v>98396</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
